--- a/site/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mover Ticket Settings</t>
+          <t>Mover Ticket Conditions</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -727,227 +727,227 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Leaver Tickets</t>
+          <t>Mover Ticket Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KHKACRS1SACB85DEV28Y1RTF</t>
+          <t>h_01KPB0D5WKDQZZP6FV9D8Y6ZRJ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KHKACRS1SACB85DEV28Y1RTF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KPB0D5WKDQZZP6FV9D8Y6ZRJ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Leaver Tickets Settings</t>
+          <t>Leaver Tickets</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KHKADH0CYDDWB04HGJNJNS4F</t>
+          <t>h_01KHKACRS1SACB85DEV28Y1RTF</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KHKADH0CYDDWB04HGJNJNS4F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KHKACRS1SACB85DEV28Y1RTF</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Leaver Tickets Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KJCB73G09AAP2EPVKAJC57MP</t>
+          <t>h_01KHKADH0CYDDWB04HGJNJNS4F</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJCB73G09AAP2EPVKAJC57MP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KHKADH0CYDDWB04HGJNJNS4F</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Reporting Settings</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KJQE7BQWB9320Z52D1SFAYKR</t>
+          <t>h_01KJCB73G09AAP2EPVKAJC57MP</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJQE7BQWB9320Z52D1SFAYKR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJCB73G09AAP2EPVKAJC57MP</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Reporting Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KHKAY5WRHT5HMSHZHYHR83QN</t>
+          <t>h_01KJQE7BQWB9320Z52D1SFAYKR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KHKAY5WRHT5HMSHZHYHR83QN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJQE7BQWB9320Z52D1SFAYKR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KJQC8TFJBRN751Y06B4EK80V</t>
+          <t>h_01KHKAY5WRHT5HMSHZHYHR83QN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJQC8TFJBRN751Y06B4EK80V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KHKAY5WRHT5HMSHZHYHR83QN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KJABQZGT4TQQN6A1V0BNHYHT</t>
+          <t>h_01KJQC8TFJBRN751Y06B4EK80V</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJABQZGT4TQQN6A1V0BNHYHT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJQC8TFJBRN751Y06B4EK80V</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KJQCVN5JXDYK99G1CY19MKJN</t>
+          <t>h_01KJABQZGT4TQQN6A1V0BNHYHT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJQCVN5JXDYK99G1CY19MKJN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJABQZGT4TQQN6A1V0BNHYHT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KJC8VW4WATPSB1M1AMK3G979</t>
+          <t>h_01KJQCVN5JXDYK99G1CY19MKJN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJC8VW4WATPSB1M1AMK3G979</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJQCVN5JXDYK99G1CY19MKJN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Admin Notification Settings</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KJQDEHPDW9JGG1XPY61Q1ZFX</t>
+          <t>h_01KJC8VW4WATPSB1M1AMK3G979</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJQDEHPDW9JGG1XPY61Q1ZFX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJC8VW4WATPSB1M1AMK3G979</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Employee Notification Settings</t>
+          <t>Admin Notification Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,63 +957,63 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KJQDTX5JSC3Q3783PK1BX5DF</t>
+          <t>h_01KJQDEHPDW9JGG1XPY61Q1ZFX</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJQDTX5JSC3Q3783PK1BX5DF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJQDEHPDW9JGG1XPY61Q1ZFX</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Employee Notification Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KHKB5JY6TY3YJQRG433GPA14</t>
+          <t>h_01KJQDTX5JSC3Q3783PK1BX5DF</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KHKB5JY6TY3YJQRG433GPA14</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJQDTX5JSC3Q3783PK1BX5DF</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Joiner</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
+          <t>h_01KHKB5JY6TY3YJQRG433GPA14</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KHKB5JY6TY3YJQRG433GPA14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mover</t>
+          <t>Joiner</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KHKBKHBP49K206ZXCYR1NSCH</t>
+          <t>h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KHKBKHBP49K206ZXCYR1NSCH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Leaver</t>
+          <t>Mover</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,63 +1045,63 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KJQF6D1P564MF3DXCXQJ0YQS</t>
+          <t>h_01KHKBKHBP49K206ZXCYR1NSCH</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJQF6D1P564MF3DXCXQJ0YQS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KHKBKHBP49K206ZXCYR1NSCH</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Leaver</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KJQF6D1P564MF3DXCXQJ0YQS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KJQF6D1P564MF3DXCXQJ0YQS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,32 +1111,54 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
